--- a/GNN-GO/output/excel_exports/Resultados optuna.xlsx
+++ b/GNN-GO/output/excel_exports/Resultados optuna.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Macarena Madrid\Desktop\alzheimer-target-prediction\GNN-GO\output\excel_exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AF1362-4FE7-4973-9B71-1DB9D6349794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACDC30C-AE0B-40B2-8AB2-E0533B169411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="top_10" sheetId="1" r:id="rId1"/>
     <sheet name="all_trials" sheetId="3" r:id="rId2"/>
     <sheet name="charts" sheetId="2" r:id="rId3"/>
+    <sheet name="Cluster" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="240">
   <si>
     <t>hidden_channels</t>
   </si>
@@ -691,6 +692,63 @@
   </si>
   <si>
     <t>0.263851</t>
+  </si>
+  <si>
+    <t>Kmeans</t>
+  </si>
+  <si>
+    <t>DBSCAN</t>
+  </si>
+  <si>
+    <t>HDBSCAN</t>
+  </si>
+  <si>
+    <t>Davies-Bouldin Index</t>
+  </si>
+  <si>
+    <t>Calinski-Harabasz</t>
+  </si>
+  <si>
+    <t>MCL (Markov Cluster Algorithm)</t>
+  </si>
+  <si>
+    <t>K = 5</t>
+  </si>
+  <si>
+    <t>Algoritmos de
+Clustering</t>
+  </si>
+  <si>
+    <t>Mejores
+Hiperparámetros</t>
+  </si>
+  <si>
+    <t>Inflation Parameter =</t>
+  </si>
+  <si>
+    <t>Silhouette score</t>
+  </si>
+  <si>
+    <t>Porcentaje de ruido</t>
+  </si>
+  <si>
+    <t>Número de clústeres</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>0.280557</t>
+  </si>
+  <si>
+    <t>Eps = 0.0064
+Min Samples = 90.0</t>
+  </si>
+  <si>
+    <t>Min_cluster_size= 20
+min_samples = 20
+cluster_selection_epsilon = 0.0
+alpha = 2.0</t>
   </si>
 </sst>
 </file>
@@ -761,7 +819,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,6 +853,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -854,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -903,6 +967,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1562,7 +1638,7 @@
             <c:numRef>
               <c:f>charts!$C$14:$V$14</c:f>
               <c:numCache>
-                <c:formatCode>000,000</c:formatCode>
+                <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.94296764033075997</c:v>
@@ -1718,7 +1794,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="000,000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6200,4 +6276,111 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DAB06C-92CF-4946-BF2D-F3013FF2D053}">
+  <dimension ref="C2:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="F2" s="24"/>
+    </row>
+    <row r="7" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="C7" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="28">
+        <v>1248037</v>
+      </c>
+      <c r="G8" s="28">
+        <v>1676695378</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="C9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="3:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="C10" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>